--- a/sharps.xlsx
+++ b/sharps.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MESS\projects\ROBOTICS\BUM-BULL-BEE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8A582664-FA02-401C-B9A2-1B98903F59D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{793C3BEA-6974-462D-A244-99C96D4B26C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{DBA7806E-EAA5-4BC3-A605-C12497C22FDB}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{DBA7806E-EAA5-4BC3-A605-C12497C22FDB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,6 +31,14 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="1">
+  <si>
+    <t>პროსტაზე</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -381,596 +389,645 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0892404-5E89-4F1F-8FED-BCD614D0E6B9}">
-  <dimension ref="A1:E80"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1">
         <v>1</v>
       </c>
       <c r="B1">
-        <v>2.4500000000000002</v>
-      </c>
-      <c r="D1">
+        <v>2.5190000000000001</v>
+      </c>
+      <c r="E1">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F1">
+        <v>1.8029999999999999</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2</v>
       </c>
       <c r="B2">
-        <v>1.73</v>
-      </c>
-      <c r="D2">
+        <v>1.9770000000000001</v>
+      </c>
+      <c r="E2">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F2">
+        <v>1.6419999999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>3</v>
       </c>
       <c r="B3">
-        <v>1.32</v>
-      </c>
-      <c r="D3">
+        <v>1.4059999999999999</v>
+      </c>
+      <c r="E3">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F3">
+        <v>2.9420000000000002</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>4</v>
       </c>
       <c r="B4">
-        <v>1.1100000000000001</v>
-      </c>
-      <c r="D4">
+        <v>1.2290000000000001</v>
+      </c>
+      <c r="E4">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F4">
+        <v>3.1480000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>5</v>
       </c>
       <c r="B5">
-        <v>1.01</v>
-      </c>
-      <c r="D5">
+        <v>1.006</v>
+      </c>
+      <c r="E5">
         <v>5</v>
       </c>
-      <c r="E5">
-        <v>3.18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F5">
+        <v>3.165</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>6</v>
       </c>
       <c r="B6">
-        <v>0.88</v>
-      </c>
-      <c r="D6">
+        <v>0.89</v>
+      </c>
+      <c r="E6">
         <v>6</v>
       </c>
-      <c r="E6">
-        <v>3.09</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F6">
+        <v>3.165</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>7</v>
       </c>
       <c r="B7">
-        <v>0.75</v>
-      </c>
-      <c r="D7">
+        <v>0.77700000000000002</v>
+      </c>
+      <c r="E7">
         <v>7</v>
       </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F7">
+        <v>3.0350000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>8</v>
       </c>
       <c r="B8">
-        <v>0.69</v>
-      </c>
-      <c r="D8">
+        <v>0.69399999999999995</v>
+      </c>
+      <c r="E8">
         <v>8</v>
       </c>
-      <c r="E8">
-        <v>2.74</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F8">
+        <v>2.726</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>9</v>
       </c>
       <c r="B9">
-        <v>0.63</v>
-      </c>
-      <c r="D9">
+        <v>0.63200000000000001</v>
+      </c>
+      <c r="E9">
         <v>9</v>
       </c>
-      <c r="E9">
-        <v>2.5499999999999998</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F9">
+        <v>2.5259999999999998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>10</v>
       </c>
       <c r="B10">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="D10">
+        <v>0.57099999999999995</v>
+      </c>
+      <c r="E10">
         <v>10</v>
       </c>
-      <c r="E10">
-        <v>2.35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F10">
+        <v>2.4159999999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>11</v>
       </c>
       <c r="B11">
-        <v>0.49</v>
-      </c>
-      <c r="D11">
+        <v>0.51600000000000001</v>
+      </c>
+      <c r="E11">
         <v>11</v>
       </c>
-      <c r="E11">
-        <v>2.08</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F11">
+        <v>2.2229999999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>12</v>
       </c>
       <c r="B12">
-        <v>0.47</v>
-      </c>
-      <c r="D12">
+        <v>0.47699999999999998</v>
+      </c>
+      <c r="E12">
         <v>12</v>
       </c>
-      <c r="E12">
-        <v>1.96</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F12">
+        <v>2.052</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>13</v>
       </c>
       <c r="B13">
-        <v>0.43</v>
-      </c>
-      <c r="D13">
+        <v>0.45500000000000002</v>
+      </c>
+      <c r="E13">
         <v>13</v>
       </c>
-      <c r="E13">
-        <v>1.81</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F13">
+        <v>1.91</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>14</v>
       </c>
       <c r="B14">
-        <v>0.39</v>
-      </c>
-      <c r="D14">
+        <v>0.41299999999999998</v>
+      </c>
+      <c r="E14">
         <v>14</v>
       </c>
-      <c r="E14">
-        <v>1.72</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F14">
+        <v>1.7709999999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>15</v>
       </c>
       <c r="B15">
-        <v>0.37</v>
-      </c>
-      <c r="D15">
+        <v>0.39400000000000002</v>
+      </c>
+      <c r="E15">
         <v>15</v>
       </c>
-      <c r="E15">
-        <v>1.65</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F15">
+        <v>1.681</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>16</v>
       </c>
       <c r="B16">
-        <v>0.35</v>
-      </c>
-      <c r="D16">
+        <v>0.374</v>
+      </c>
+      <c r="E16">
         <v>16</v>
       </c>
-      <c r="E16">
-        <v>1.58</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F16">
+        <v>1.587</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>17</v>
       </c>
       <c r="B17">
-        <v>0.31</v>
-      </c>
-      <c r="D17">
+        <v>0.33200000000000002</v>
+      </c>
+      <c r="E17">
         <v>17</v>
       </c>
-      <c r="E17">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F17">
+        <v>1.506</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>18</v>
       </c>
       <c r="B18">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="D18">
+        <v>0.33200000000000002</v>
+      </c>
+      <c r="E18">
         <v>18</v>
       </c>
-      <c r="E18">
-        <v>1.48</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F18">
+        <v>1.4259999999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>19</v>
       </c>
       <c r="B19">
-        <v>0.27</v>
-      </c>
-      <c r="D19">
+        <v>0.313</v>
+      </c>
+      <c r="E19">
         <v>19</v>
       </c>
-      <c r="E19">
-        <v>1.37</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F19">
+        <v>1.365</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>20</v>
       </c>
       <c r="B20">
-        <v>0.25</v>
-      </c>
-      <c r="D20">
+        <v>0.29399999999999998</v>
+      </c>
+      <c r="E20">
         <v>20</v>
       </c>
-      <c r="E20">
-        <v>1.31</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D21">
+      <c r="F20">
+        <v>1.2809999999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>0</v>
+      </c>
+      <c r="B21">
+        <v>1.9E-2</v>
+      </c>
+      <c r="E21">
         <v>21</v>
       </c>
-      <c r="E21">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D22">
+      <c r="F21">
+        <v>1.2230000000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E22">
         <v>22</v>
       </c>
-      <c r="E22">
-        <v>1.23</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D23">
+      <c r="F22">
+        <v>1.161</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E23">
         <v>23</v>
       </c>
-      <c r="E23">
-        <v>1.1599999999999999</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D24">
+      <c r="F23">
+        <v>1.129</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E24">
         <v>24</v>
       </c>
-      <c r="E24">
-        <v>1.1100000000000001</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D25">
+      <c r="F24">
+        <v>1.0840000000000001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E25">
         <v>25</v>
       </c>
-      <c r="E25">
-        <v>1.05</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D26">
+      <c r="F25">
+        <v>1.0289999999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E26">
         <v>26</v>
       </c>
-      <c r="E26">
-        <v>1.01</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D27">
+      <c r="F26">
+        <v>1.006</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E27">
         <v>27</v>
       </c>
-      <c r="E27">
-        <v>0.97</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D28">
+      <c r="F27">
+        <v>0.97399999999999998</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E28">
         <v>28</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D29">
+      <c r="F28">
+        <v>0.93899999999999995</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E29">
         <v>29</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D30">
+      <c r="F29">
+        <v>0.92300000000000004</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E30">
         <v>30</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D31">
+      <c r="F30">
+        <v>0.88400000000000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E31">
         <v>31</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D32">
+      <c r="F31">
+        <v>0.84499999999999997</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E32">
         <v>32</v>
       </c>
-    </row>
-    <row r="33" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D33">
+      <c r="F32">
+        <v>0.82899999999999996</v>
+      </c>
+    </row>
+    <row r="33" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E33">
         <v>33</v>
       </c>
-    </row>
-    <row r="34" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D34">
+      <c r="F33">
+        <v>0.80600000000000005</v>
+      </c>
+    </row>
+    <row r="34" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E34">
         <v>34</v>
       </c>
-    </row>
-    <row r="35" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D35">
+      <c r="F34">
+        <v>0.78700000000000003</v>
+      </c>
+    </row>
+    <row r="35" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E35">
         <v>35</v>
       </c>
-    </row>
-    <row r="36" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D36">
+      <c r="F35">
+        <v>0.76500000000000001</v>
+      </c>
+    </row>
+    <row r="36" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E36">
         <v>36</v>
       </c>
-    </row>
-    <row r="37" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D37">
+      <c r="F36">
+        <v>0.745</v>
+      </c>
+    </row>
+    <row r="37" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E37">
         <v>37</v>
       </c>
-    </row>
-    <row r="38" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D38">
+      <c r="F37">
+        <v>0.72299999999999998</v>
+      </c>
+    </row>
+    <row r="38" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E38">
         <v>38</v>
       </c>
-    </row>
-    <row r="39" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D39">
+      <c r="F38">
+        <v>0.70299999999999996</v>
+      </c>
+    </row>
+    <row r="39" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E39">
         <v>39</v>
       </c>
-    </row>
-    <row r="40" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D40">
+      <c r="F39">
+        <v>0.68400000000000005</v>
+      </c>
+    </row>
+    <row r="40" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E40">
         <v>40</v>
       </c>
-    </row>
-    <row r="41" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D41">
+      <c r="F40">
+        <v>0.66500000000000004</v>
+      </c>
+    </row>
+    <row r="41" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E41">
         <v>41</v>
       </c>
-    </row>
-    <row r="42" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D42">
+      <c r="F41">
+        <v>0.64500000000000002</v>
+      </c>
+    </row>
+    <row r="42" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E42">
         <v>42</v>
       </c>
-    </row>
-    <row r="43" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D43">
+      <c r="F42">
+        <v>0.63900000000000001</v>
+      </c>
+    </row>
+    <row r="43" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E43">
         <v>43</v>
       </c>
-    </row>
-    <row r="44" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D44">
+      <c r="F43">
+        <v>0.623</v>
+      </c>
+    </row>
+    <row r="44" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E44">
         <v>44</v>
       </c>
-    </row>
-    <row r="45" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D45">
+      <c r="F44">
+        <v>0.61599999999999999</v>
+      </c>
+    </row>
+    <row r="45" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E45">
         <v>45</v>
       </c>
-    </row>
-    <row r="46" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D46">
+      <c r="F45">
+        <v>0.60299999999999998</v>
+      </c>
+    </row>
+    <row r="46" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E46">
         <v>46</v>
       </c>
-    </row>
-    <row r="47" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D47">
+      <c r="F46">
+        <v>0.59699999999999998</v>
+      </c>
+    </row>
+    <row r="47" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E47">
         <v>47</v>
       </c>
-    </row>
-    <row r="48" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D48">
+      <c r="F47">
+        <v>0.58399999999999996</v>
+      </c>
+    </row>
+    <row r="48" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E48">
         <v>48</v>
       </c>
-    </row>
-    <row r="49" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D49">
+      <c r="F48">
+        <v>0.56499999999999995</v>
+      </c>
+    </row>
+    <row r="49" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E49">
         <v>49</v>
       </c>
-    </row>
-    <row r="50" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D50">
+      <c r="F49">
+        <v>0.55800000000000005</v>
+      </c>
+    </row>
+    <row r="50" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E50">
         <v>50</v>
       </c>
-    </row>
-    <row r="51" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D51">
+      <c r="F50">
+        <v>0.54500000000000004</v>
+      </c>
+    </row>
+    <row r="51" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E51">
         <v>51</v>
       </c>
-    </row>
-    <row r="52" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D52">
+      <c r="F51">
+        <v>0.52300000000000002</v>
+      </c>
+    </row>
+    <row r="52" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E52">
         <v>52</v>
       </c>
-    </row>
-    <row r="53" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D53">
+      <c r="F52">
+        <v>0.51900000000000002</v>
+      </c>
+    </row>
+    <row r="53" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E53">
         <v>53</v>
       </c>
-    </row>
-    <row r="54" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D54">
+      <c r="F53">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="54" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E54">
         <v>54</v>
       </c>
-    </row>
-    <row r="55" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D55">
+      <c r="F54">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="55" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E55">
         <v>55</v>
       </c>
-    </row>
-    <row r="56" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D56">
+      <c r="F55">
+        <v>0.497</v>
+      </c>
+    </row>
+    <row r="56" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E56">
         <v>56</v>
       </c>
-    </row>
-    <row r="57" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D57">
+      <c r="F56">
+        <v>0.495</v>
+      </c>
+    </row>
+    <row r="57" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E57">
         <v>57</v>
       </c>
-    </row>
-    <row r="58" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D58">
+      <c r="F57">
+        <v>0.48399999999999999</v>
+      </c>
+    </row>
+    <row r="58" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E58">
         <v>58</v>
       </c>
-    </row>
-    <row r="59" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D59">
+      <c r="F58">
+        <v>0.46800000000000003</v>
+      </c>
+    </row>
+    <row r="59" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E59">
         <v>59</v>
       </c>
-    </row>
-    <row r="60" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D60">
+      <c r="F59">
+        <v>0.45700000000000002</v>
+      </c>
+    </row>
+    <row r="60" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E60">
         <v>60</v>
       </c>
-    </row>
-    <row r="61" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D61">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="62" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D62">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="63" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D63">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="64" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D64">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="65" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D65">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="66" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D66">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="67" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D67">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="68" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D68">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="69" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D69">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="70" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D70">
+      <c r="F60">
+        <v>0.442</v>
+      </c>
+    </row>
+    <row r="61" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E61">
         <v>70</v>
       </c>
-    </row>
-    <row r="71" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D71">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="72" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D72">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="73" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D73">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="74" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D74">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="75" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D75">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="76" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D76">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="77" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D77">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="78" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D78">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="79" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D79">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="80" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D80">
+      <c r="F61">
+        <v>0.39700000000000002</v>
+      </c>
+    </row>
+    <row r="62" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E62">
         <v>80</v>
+      </c>
+      <c r="F62">
+        <v>0.34499999999999997</v>
+      </c>
+    </row>
+    <row r="63" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E63">
+        <v>90</v>
+      </c>
+      <c r="F63">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="64" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E64" t="s">
+        <v>0</v>
+      </c>
+      <c r="F64">
+        <v>0.216</v>
       </c>
     </row>
   </sheetData>
